--- a/frontend/data/plantilla-agente-utopia.xlsx
+++ b/frontend/data/plantilla-agente-utopia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mriverius/Downloads/Repositories/travel-pioneers/frontend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5796C1-EFE3-E142-83EB-676635CE6BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC3FD2B-3FCE-7A47-98B7-7C5B175572A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{705A2A06-CCAF-4902-AE72-D82AD645FD9B}"/>
   </bookViews>
@@ -445,7 +445,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="207">
   <si>
     <t xml:space="preserve">Razon social </t>
   </si>
@@ -1063,6 +1063,9 @@
   </si>
   <si>
     <t>MONEDA 3</t>
+  </si>
+  <si>
+    <t>NOTAS</t>
   </si>
 </sst>
 </file>
@@ -2041,7 +2044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C72AF7-A35A-4F3C-B64F-81CB8265B30E}">
-  <dimension ref="A1:AZ60"/>
+  <dimension ref="A1:BA60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
@@ -2084,31 +2087,31 @@
     <col min="50" max="50" width="19.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
       <c r="B1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A2" s="11"/>
       <c r="B2" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A3" s="12"/>
       <c r="B3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
       <c r="B4" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:52" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:53" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
@@ -2265,8 +2268,11 @@
       <c r="AZ6" s="5" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="BA6" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -2286,7 +2292,7 @@
       <c r="AH7" s="2"/>
       <c r="AO7" s="16"/>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -2305,7 +2311,7 @@
       <c r="AG8" s="8"/>
       <c r="AH8" s="2"/>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -2324,7 +2330,7 @@
       <c r="AG9" s="8"/>
       <c r="AH9" s="2"/>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -2343,7 +2349,7 @@
       <c r="AG10" s="8"/>
       <c r="AH10" s="2"/>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -2362,7 +2368,7 @@
       <c r="AG11" s="8"/>
       <c r="AH11" s="2"/>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -2381,7 +2387,7 @@
       <c r="AG12" s="8"/>
       <c r="AH12" s="2"/>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -2400,7 +2406,7 @@
       <c r="AG13" s="8"/>
       <c r="AH13" s="2"/>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -2419,7 +2425,7 @@
       <c r="AG14" s="8"/>
       <c r="AH14" s="2"/>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -2438,7 +2444,7 @@
       <c r="AG15" s="8"/>
       <c r="AH15" s="2"/>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
